--- a/config/notice.xlsx
+++ b/config/notice.xlsx
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>ガチャ</t>
+          <t>抽卡</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>強力な仲間を集めて、戦力を一気にアップ！</t>
+          <t>收集强力的伙伴，一口气提升战力！</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>編成</t>
+          <t>编队</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>編成位置を調整して、勝利の陣形を築け！</t>
+          <t>调整阵型位置，打造胜利阵形！</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>キャラ突破で潜在力を限界まで解放！</t>
+          <t>突破角色将潜力释放到极限！</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>スキル強化</t>
+          <t>技能强化</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>スキル強化で、必殺技の威力がさらにアップ！</t>
+          <t>技能强化，必杀技威力更上一层楼！</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>レベルアップ</t>
+          <t>升级</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>キャラレベル高速成長！最強への道を駆け抜けろ！</t>
+          <t>角色等级高速成长！奔向最强之路！</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>ショップ</t>
+          <t>商店</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>ショップ解放！欲しいアイテム、ここに集結！</t>
+          <t>商店解放！想要的物品，在这里集合！</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>図鑑</t>
+          <t>图鉴</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>新たな仲間と出会って、図鑑も絆もコンプリート！</t>
+          <t>与新伙伴相遇，完成图鉴与羁绊！</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>装備</t>
+          <t>装备</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>装備道具を装備し、追加効果を獲得せよ！</t>
+          <t>装备道具，获得额外效果！</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>毎日任務</t>
+          <t>每日任务</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>毎日任務で報酬ゲット！日々の積み重ねが勝利を呼ぶ！</t>
+          <t>每日任务奖励！每一天的积累都会带来胜利！</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>ライセンス</t>
+          <t>许可证</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>ライセンスを上げ、さらなる特権を解放！</t>
+          <t>获得许可证并释放更多特权！</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>能力値</t>
+          <t>能力值</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>能力値をリセットして、理想の仲間を育成！</t>
+          <t>重置能力值，培养理想的伙伴！</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>アリーナ</t>
+          <t>竞技场</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>アリーナ解放！今こそ腕試しのとき！</t>
+          <t>竞技场解放！现在正是考验实力的时候！</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>順位</t>
+          <t>排名</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>順位公開！自分の順位を確認せよ！</t>
+          <t>排名公开！检查自己的排名！</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>日常ダンジョン</t>
+          <t>日常地牢</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>日常ダンジョンで資源を手に入れよう！</t>
+          <t>在日常地下城获取资源！</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>ギルド</t>
+          <t>公会</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>ギルド解放！仲間と共に戦え！</t>
+          <t>公会解放！与伙伴一起战斗吧！</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>交換</t>
+          <t>交换</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>性格＆能力値は継承可能！理想の育成を次世代へ！</t>
+          <t>性格和能力值可以继承！培养下一代的理想！</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>リセット</t>
+          <t>重置</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>キャラリセットで育成素材を即時返還！</t>
+          <t>角色重置可立即返还育成素材！</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>試練の道に挑戦し、限界のその先へ！</t>
+          <t>挑战考验之路，迈向极限的前方！</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>強化値</t>
+          <t>强化值</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>強化値＆効果アップでパワー全開！</t>
+          <t>强化值&amp;效果提升，力量全开！</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>仲間にギフトを贈って、好感度アップ！</t>
+          <t>赠送礼物给伙伴，提高好感度！</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2852,14 +2852,14 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
+          <t>天赋</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>天賦</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>天賦</t>
-        </is>
-      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>Talent</t>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>天賦解放！キャラの真の力が目覚める！</t>
+          <t>天赋解放！角色真正的力量觉醒！</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>派遣システム解放！サクッと報酬獲得！</t>
+          <t>派遣系统开放！快速获得奖励！</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
